--- a/AAII_Financials/Yearly/CZOO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CZOO_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -715,13 +715,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1549000</v>
+        <v>1592100</v>
       </c>
       <c r="E8" s="3">
-        <v>813100</v>
+        <v>835700</v>
       </c>
       <c r="F8" s="3">
-        <v>201200</v>
+        <v>206800</v>
       </c>
       <c r="G8" s="3">
         <v>1500</v>
@@ -748,16 +748,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1523900</v>
+        <v>1566200</v>
       </c>
       <c r="E9" s="3">
-        <v>784200</v>
+        <v>806000</v>
       </c>
       <c r="F9" s="3">
-        <v>204800</v>
+        <v>210500</v>
       </c>
       <c r="G9" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -781,16 +781,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>25100</v>
+        <v>25800</v>
       </c>
       <c r="E10" s="3">
-        <v>28900</v>
+        <v>29700</v>
       </c>
       <c r="F10" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="G10" s="3">
-        <v>-1300</v>
+        <v>-1400</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -895,10 +895,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>384800</v>
+        <v>395500</v>
       </c>
       <c r="E14" s="3">
-        <v>55500</v>
+        <v>57000</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -928,10 +928,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>62500</v>
+        <v>64200</v>
       </c>
       <c r="E15" s="3">
-        <v>64100</v>
+        <v>65900</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>3</v>
@@ -973,16 +973,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2378300</v>
+        <v>2444500</v>
       </c>
       <c r="E17" s="3">
-        <v>1201300</v>
+        <v>1234700</v>
       </c>
       <c r="F17" s="3">
-        <v>324100</v>
+        <v>333100</v>
       </c>
       <c r="G17" s="3">
-        <v>23400</v>
+        <v>24000</v>
       </c>
       <c r="H17" s="3">
         <v>200</v>
@@ -1006,16 +1006,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-829300</v>
+        <v>-852400</v>
       </c>
       <c r="E18" s="3">
-        <v>-388200</v>
+        <v>-399000</v>
       </c>
       <c r="F18" s="3">
-        <v>-122900</v>
+        <v>-126300</v>
       </c>
       <c r="G18" s="3">
-        <v>-21900</v>
+        <v>-22500</v>
       </c>
       <c r="H18" s="3">
         <v>-200</v>
@@ -1054,10 +1054,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>243600</v>
+        <v>250400</v>
       </c>
       <c r="E20" s="3">
-        <v>-259900</v>
+        <v>-267200</v>
       </c>
       <c r="F20" s="3">
         <v>600</v>
@@ -1087,16 +1087,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-113700</v>
+        <v>-115600</v>
       </c>
       <c r="E21" s="3">
-        <v>-567700</v>
+        <v>-583200</v>
       </c>
       <c r="F21" s="3">
-        <v>-106100</v>
+        <v>-109000</v>
       </c>
       <c r="G21" s="3">
-        <v>-20800</v>
+        <v>-21300</v>
       </c>
       <c r="H21" s="3">
         <v>-200</v>
@@ -1120,13 +1120,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>66200</v>
+        <v>68000</v>
       </c>
       <c r="E22" s="3">
-        <v>11200</v>
+        <v>11500</v>
       </c>
       <c r="F22" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G22" s="3">
         <v>600</v>
@@ -1153,16 +1153,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-651900</v>
+        <v>-670000</v>
       </c>
       <c r="E23" s="3">
-        <v>-659300</v>
+        <v>-677700</v>
       </c>
       <c r="F23" s="3">
-        <v>-123900</v>
+        <v>-127300</v>
       </c>
       <c r="G23" s="3">
-        <v>-22300</v>
+        <v>-22900</v>
       </c>
       <c r="H23" s="3">
         <v>-200</v>
@@ -1186,10 +1186,10 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-9100</v>
+        <v>-9400</v>
       </c>
       <c r="E24" s="3">
-        <v>-2700</v>
+        <v>-2800</v>
       </c>
       <c r="F24" s="3">
         <v>-1200</v>
@@ -1252,16 +1252,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-642800</v>
+        <v>-660700</v>
       </c>
       <c r="E26" s="3">
-        <v>-656600</v>
+        <v>-674900</v>
       </c>
       <c r="F26" s="3">
-        <v>-122700</v>
+        <v>-126100</v>
       </c>
       <c r="G26" s="3">
-        <v>-22300</v>
+        <v>-22900</v>
       </c>
       <c r="H26" s="3">
         <v>-200</v>
@@ -1285,16 +1285,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-642800</v>
+        <v>-660700</v>
       </c>
       <c r="E27" s="3">
-        <v>-656600</v>
+        <v>-674900</v>
       </c>
       <c r="F27" s="3">
-        <v>-122700</v>
+        <v>-126100</v>
       </c>
       <c r="G27" s="3">
-        <v>-22300</v>
+        <v>-22900</v>
       </c>
       <c r="H27" s="3">
         <v>-200</v>
@@ -1351,13 +1351,13 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-230500</v>
+        <v>-236900</v>
       </c>
       <c r="E29" s="3">
-        <v>-17600</v>
+        <v>-18100</v>
       </c>
       <c r="F29" s="3">
-        <v>-4700</v>
+        <v>-4900</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1450,10 +1450,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-243600</v>
+        <v>-250400</v>
       </c>
       <c r="E32" s="3">
-        <v>259900</v>
+        <v>267200</v>
       </c>
       <c r="F32" s="3">
         <v>-600</v>
@@ -1483,16 +1483,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-873200</v>
+        <v>-897500</v>
       </c>
       <c r="E33" s="3">
-        <v>-674300</v>
+        <v>-693000</v>
       </c>
       <c r="F33" s="3">
-        <v>-127400</v>
+        <v>-130900</v>
       </c>
       <c r="G33" s="3">
-        <v>-22300</v>
+        <v>-22900</v>
       </c>
       <c r="H33" s="3">
         <v>-200</v>
@@ -1549,16 +1549,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-873200</v>
+        <v>-897500</v>
       </c>
       <c r="E35" s="3">
-        <v>-674300</v>
+        <v>-693000</v>
       </c>
       <c r="F35" s="3">
-        <v>-127400</v>
+        <v>-130900</v>
       </c>
       <c r="G35" s="3">
-        <v>-22300</v>
+        <v>-22900</v>
       </c>
       <c r="H35" s="3">
         <v>-200</v>
@@ -1650,19 +1650,19 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>305000</v>
+        <v>313500</v>
       </c>
       <c r="E41" s="3">
-        <v>239000</v>
+        <v>245600</v>
       </c>
       <c r="F41" s="3">
-        <v>302100</v>
+        <v>310500</v>
       </c>
       <c r="G41" s="3">
-        <v>42800</v>
+        <v>44000</v>
       </c>
       <c r="H41" s="3">
-        <v>32700</v>
+        <v>33600</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1749,16 +1749,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>288500</v>
+        <v>296500</v>
       </c>
       <c r="E44" s="3">
-        <v>452300</v>
+        <v>464900</v>
       </c>
       <c r="F44" s="3">
-        <v>142300</v>
+        <v>146200</v>
       </c>
       <c r="G44" s="3">
-        <v>53300</v>
+        <v>54800</v>
       </c>
       <c r="H44" s="3">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>81600</v>
+        <v>83900</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -1815,19 +1815,19 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>745000</v>
+        <v>765700</v>
       </c>
       <c r="E46" s="3">
-        <v>787900</v>
+        <v>809800</v>
       </c>
       <c r="F46" s="3">
-        <v>480800</v>
+        <v>494200</v>
       </c>
       <c r="G46" s="3">
-        <v>112600</v>
+        <v>115700</v>
       </c>
       <c r="H46" s="3">
-        <v>32800</v>
+        <v>33700</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1848,19 +1848,19 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="E47" s="3">
-        <v>12400</v>
+        <v>12700</v>
       </c>
       <c r="F47" s="3">
-        <v>9300</v>
+        <v>9600</v>
       </c>
       <c r="G47" s="3">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="H47" s="3">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1881,16 +1881,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>299600</v>
+        <v>308000</v>
       </c>
       <c r="E48" s="3">
-        <v>338900</v>
+        <v>348400</v>
       </c>
       <c r="F48" s="3">
-        <v>106600</v>
+        <v>109600</v>
       </c>
       <c r="G48" s="3">
-        <v>10900</v>
+        <v>11200</v>
       </c>
       <c r="H48" s="3">
         <v>0</v>
@@ -1914,16 +1914,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>20300</v>
+        <v>20900</v>
       </c>
       <c r="E49" s="3">
-        <v>324400</v>
+        <v>333500</v>
       </c>
       <c r="F49" s="3">
-        <v>33100</v>
+        <v>34000</v>
       </c>
       <c r="G49" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -2079,19 +2079,19 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1073000</v>
+        <v>1102800</v>
       </c>
       <c r="E54" s="3">
-        <v>1463600</v>
+        <v>1504300</v>
       </c>
       <c r="F54" s="3">
-        <v>629800</v>
+        <v>647300</v>
       </c>
       <c r="G54" s="3">
-        <v>132400</v>
+        <v>136100</v>
       </c>
       <c r="H54" s="3">
-        <v>39000</v>
+        <v>40100</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -2142,16 +2142,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>22500</v>
+        <v>23100</v>
       </c>
       <c r="E57" s="3">
-        <v>36300</v>
+        <v>37300</v>
       </c>
       <c r="F57" s="3">
-        <v>15700</v>
+        <v>16200</v>
       </c>
       <c r="G57" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
@@ -2175,16 +2175,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>239400</v>
+        <v>246100</v>
       </c>
       <c r="E58" s="3">
-        <v>234700</v>
+        <v>241200</v>
       </c>
       <c r="F58" s="3">
-        <v>117400</v>
+        <v>120600</v>
       </c>
       <c r="G58" s="3">
-        <v>42200</v>
+        <v>43300</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2208,16 +2208,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>162700</v>
+        <v>167300</v>
       </c>
       <c r="E59" s="3">
-        <v>74700</v>
+        <v>76800</v>
       </c>
       <c r="F59" s="3">
-        <v>28400</v>
+        <v>29200</v>
       </c>
       <c r="G59" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="H59" s="3">
         <v>0</v>
@@ -2241,16 +2241,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>424700</v>
+        <v>436500</v>
       </c>
       <c r="E60" s="3">
-        <v>345700</v>
+        <v>355300</v>
       </c>
       <c r="F60" s="3">
-        <v>161500</v>
+        <v>166000</v>
       </c>
       <c r="G60" s="3">
-        <v>47500</v>
+        <v>48800</v>
       </c>
       <c r="H60" s="3">
         <v>100</v>
@@ -2274,16 +2274,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>546800</v>
+        <v>562000</v>
       </c>
       <c r="E61" s="3">
-        <v>173300</v>
+        <v>178100</v>
       </c>
       <c r="F61" s="3">
-        <v>54100</v>
+        <v>55600</v>
       </c>
       <c r="G61" s="3">
-        <v>5400</v>
+        <v>5600</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2307,13 +2307,13 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11500</v>
+        <v>11800</v>
       </c>
       <c r="E62" s="3">
-        <v>63000</v>
+        <v>64700</v>
       </c>
       <c r="F62" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="G62" s="3">
         <v>700</v>
@@ -2439,16 +2439,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>982900</v>
+        <v>1010300</v>
       </c>
       <c r="E66" s="3">
-        <v>582000</v>
+        <v>598100</v>
       </c>
       <c r="F66" s="3">
-        <v>219800</v>
+        <v>225900</v>
       </c>
       <c r="G66" s="3">
-        <v>53500</v>
+        <v>55000</v>
       </c>
       <c r="H66" s="3">
         <v>100</v>
@@ -2619,16 +2619,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1064400</v>
+        <v>-1094000</v>
       </c>
       <c r="E72" s="3">
-        <v>-236200</v>
+        <v>-242700</v>
       </c>
       <c r="F72" s="3">
-        <v>79900</v>
+        <v>82100</v>
       </c>
       <c r="G72" s="3">
-        <v>-22300</v>
+        <v>-22900</v>
       </c>
       <c r="H72" s="3">
         <v>-200</v>
@@ -2751,19 +2751,19 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>90100</v>
+        <v>92600</v>
       </c>
       <c r="E76" s="3">
-        <v>881700</v>
+        <v>906200</v>
       </c>
       <c r="F76" s="3">
-        <v>410000</v>
+        <v>421400</v>
       </c>
       <c r="G76" s="3">
-        <v>78800</v>
+        <v>81000</v>
       </c>
       <c r="H76" s="3">
-        <v>38900</v>
+        <v>39900</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2855,16 +2855,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-873200</v>
+        <v>-897500</v>
       </c>
       <c r="E81" s="3">
-        <v>-674300</v>
+        <v>-693000</v>
       </c>
       <c r="F81" s="3">
-        <v>-127400</v>
+        <v>-130900</v>
       </c>
       <c r="G81" s="3">
-        <v>-22300</v>
+        <v>-22900</v>
       </c>
       <c r="H81" s="3">
         <v>-200</v>
@@ -2903,13 +2903,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>471600</v>
+        <v>484700</v>
       </c>
       <c r="E83" s="3">
-        <v>80400</v>
+        <v>82600</v>
       </c>
       <c r="F83" s="3">
-        <v>16200</v>
+        <v>16600</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
@@ -3101,16 +3101,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-310600</v>
+        <v>-319300</v>
       </c>
       <c r="E89" s="3">
-        <v>-690400</v>
+        <v>-709600</v>
       </c>
       <c r="F89" s="3">
-        <v>-143800</v>
+        <v>-147800</v>
       </c>
       <c r="G89" s="3">
-        <v>-83800</v>
+        <v>-86100</v>
       </c>
       <c r="H89" s="3">
         <v>-100</v>
@@ -3149,16 +3149,16 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-41700</v>
+        <v>-42900</v>
       </c>
       <c r="E91" s="3">
-        <v>-36600</v>
+        <v>-37600</v>
       </c>
       <c r="F91" s="3">
-        <v>-22200</v>
+        <v>-22800</v>
       </c>
       <c r="G91" s="3">
-        <v>-3000</v>
+        <v>-3100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -3248,16 +3248,16 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-93700</v>
+        <v>-96300</v>
       </c>
       <c r="E94" s="3">
-        <v>-291100</v>
+        <v>-299200</v>
       </c>
       <c r="F94" s="3">
-        <v>-45100</v>
+        <v>-46300</v>
       </c>
       <c r="G94" s="3">
-        <v>-7000</v>
+        <v>-7200</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -3428,19 +3428,19 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>471800</v>
+        <v>485000</v>
       </c>
       <c r="E100" s="3">
-        <v>919300</v>
+        <v>944900</v>
       </c>
       <c r="F100" s="3">
-        <v>448100</v>
+        <v>460600</v>
       </c>
       <c r="G100" s="3">
-        <v>101000</v>
+        <v>103800</v>
       </c>
       <c r="H100" s="3">
-        <v>32900</v>
+        <v>33800</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3461,7 +3461,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>14000</v>
+        <v>14400</v>
       </c>
       <c r="E101" s="3">
         <v>-1000</v>
@@ -3494,19 +3494,19 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>81500</v>
+        <v>83800</v>
       </c>
       <c r="E102" s="3">
-        <v>-63100</v>
+        <v>-64900</v>
       </c>
       <c r="F102" s="3">
-        <v>259300</v>
+        <v>266500</v>
       </c>
       <c r="G102" s="3">
-        <v>10100</v>
+        <v>10400</v>
       </c>
       <c r="H102" s="3">
-        <v>32700</v>
+        <v>33600</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
